--- a/exports/trend_1d/IOC_full_report.xlsx
+++ b/exports/trend_1d/IOC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q87"/>
+  <dimension ref="A1:U87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>8.48</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>37.61</v>
+        <v>36.33</v>
       </c>
       <c r="I2" t="n">
         <v>37.10413221162974</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.42</v>
+        <v>-6.7</v>
       </c>
       <c r="L2" t="n">
-        <v>4.39</v>
+        <v>7.32</v>
       </c>
       <c r="M2" t="n">
-        <v>0.75</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
         <v>3.61</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>13.82</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42062</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>38.56</v>
+        <v>41.27</v>
       </c>
       <c r="I3" t="n">
         <v>40.35969838951278</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.14</v>
+        <v>-13.6</v>
       </c>
       <c r="L3" t="n">
-        <v>11.64</v>
+        <v>15.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.91</v>
+        <v>2.07</v>
       </c>
       <c r="N3" t="n">
-        <v>6.21</v>
+        <v>7.03</v>
       </c>
       <c r="O3" t="n">
         <v>-3.4</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>14.81</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42129</v>
+        <v>42130</v>
       </c>
       <c r="H4" t="n">
-        <v>43.4</v>
+        <v>38.99</v>
       </c>
       <c r="I4" t="n">
         <v>40.79965701102151</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K4" t="n">
-        <v>5.16</v>
+        <v>-5.52</v>
       </c>
       <c r="L4" t="n">
-        <v>5.31</v>
+        <v>6.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>5.76</v>
+        <v>10.16</v>
       </c>
       <c r="O4" t="n">
         <v>7.03</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>20.69</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42172</v>
+        <v>42173</v>
       </c>
       <c r="H5" t="n">
-        <v>41.41</v>
+        <v>45.02</v>
       </c>
       <c r="I5" t="n">
         <v>43.79832025569148</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.21</v>
+        <v>-15.47</v>
       </c>
       <c r="L5" t="n">
-        <v>15.59</v>
+        <v>16.31</v>
       </c>
       <c r="M5" t="n">
         <v>1.22</v>
       </c>
       <c r="N5" t="n">
-        <v>4.59</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>-10.16</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>15.22</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42221</v>
+        <v>42222</v>
       </c>
       <c r="H6" t="n">
-        <v>52.75</v>
+        <v>52.09</v>
       </c>
       <c r="I6" t="n">
         <v>52.5898417030516</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>17.17</v>
+        <v>15.7</v>
       </c>
       <c r="L6" t="n">
         <v>7.29</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>13.14</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42331</v>
+        <v>42332</v>
       </c>
       <c r="H7" t="n">
-        <v>50.95</v>
+        <v>52</v>
       </c>
       <c r="I7" t="n">
         <v>51.97543446377235</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K7" t="n">
-        <v>2.19</v>
+        <v>0.17</v>
       </c>
       <c r="L7" t="n">
         <v>6.66</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H8" t="n">
-        <v>53.28</v>
+        <v>51.76</v>
       </c>
       <c r="I8" t="n">
         <v>52.00430448875692</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K8" t="n">
-        <v>2.46</v>
+        <v>-0.46</v>
       </c>
       <c r="L8" t="n">
         <v>2.65</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>13.75</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42465</v>
+        <v>42466</v>
       </c>
       <c r="H9" t="n">
-        <v>49.44</v>
+        <v>50.76</v>
       </c>
       <c r="I9" t="n">
         <v>50.19953811475729</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K9" t="n">
-        <v>4.48</v>
+        <v>1.93</v>
       </c>
       <c r="L9" t="n">
         <v>5.31</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.34</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42510</v>
+        <v>42513</v>
       </c>
       <c r="H10" t="n">
-        <v>50.57</v>
+        <v>49.76</v>
       </c>
       <c r="I10" t="n">
         <v>49.96749229765261</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.37</v>
+        <v>-1.97</v>
       </c>
       <c r="L10" t="n">
         <v>4.49</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.49</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42548</v>
+        <v>42549</v>
       </c>
       <c r="H11" t="n">
-        <v>52.42</v>
+        <v>54.61</v>
       </c>
       <c r="I11" t="n">
         <v>53.72821224863583</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.35</v>
+        <v>-9.75</v>
       </c>
       <c r="L11" t="n">
         <v>10.03</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42685</v>
+        <v>42689</v>
       </c>
       <c r="H12" t="n">
-        <v>83.95999999999999</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>81.69548966644257</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K12" t="n">
-        <v>53.74</v>
+        <v>39.55</v>
       </c>
       <c r="L12" t="n">
         <v>3.13</v>
@@ -1125,7 +1268,7 @@
         <v>8.220000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>5.55</v>
+        <v>9.23</v>
       </c>
       <c r="O12" t="n">
         <v>4.18</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>19.95</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42732</v>
+        <v>42733</v>
       </c>
       <c r="H13" t="n">
-        <v>85.86</v>
+        <v>87.98999999999999</v>
       </c>
       <c r="I13" t="n">
         <v>87.65151690165672</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K13" t="n">
-        <v>-12.66</v>
+        <v>-15.46</v>
       </c>
       <c r="L13" t="n">
-        <v>14.77</v>
+        <v>16.39</v>
       </c>
       <c r="M13" t="n">
         <v>2.63</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.83</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42900</v>
+        <v>42901</v>
       </c>
       <c r="H14" t="n">
-        <v>118.95</v>
+        <v>114.63</v>
       </c>
       <c r="I14" t="n">
         <v>116.5157644227005</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K14" t="n">
-        <v>35.19</v>
+        <v>30.28</v>
       </c>
       <c r="L14" t="n">
         <v>2.32</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>11.24</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42950</v>
+        <v>42951</v>
       </c>
       <c r="H15" t="n">
-        <v>108.27</v>
+        <v>118.38</v>
       </c>
       <c r="I15" t="n">
         <v>109.6232397532853</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K15" t="n">
-        <v>5.55</v>
+        <v>-3.27</v>
       </c>
       <c r="L15" t="n">
-        <v>4.48</v>
+        <v>5.43</v>
       </c>
       <c r="M15" t="n">
-        <v>1.42</v>
+        <v>2.32</v>
       </c>
       <c r="N15" t="n">
-        <v>5.21</v>
+        <v>9.34</v>
       </c>
       <c r="O15" t="n">
         <v>-3.63</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>12.53</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H16" t="n">
-        <v>116.58</v>
+        <v>115.05</v>
       </c>
       <c r="I16" t="n">
         <v>116.1968572878341</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.52</v>
+        <v>-2.81</v>
       </c>
       <c r="L16" t="n">
         <v>6.94</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>9.99</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43033</v>
+        <v>43034</v>
       </c>
       <c r="H17" t="n">
-        <v>117.86</v>
+        <v>123.94</v>
       </c>
       <c r="I17" t="n">
         <v>122.4262817927578</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.44</v>
+        <v>-7.73</v>
       </c>
       <c r="L17" t="n">
-        <v>4.38</v>
+        <v>8.67</v>
       </c>
       <c r="M17" t="n">
         <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.65</v>
+        <v>5.16</v>
       </c>
       <c r="O17" t="n">
         <v>-1.31</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>10.83</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43052</v>
+        <v>43053</v>
       </c>
       <c r="H18" t="n">
-        <v>111.41</v>
+        <v>108.27</v>
       </c>
       <c r="I18" t="n">
         <v>110.5124238171434</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
-        <v>-10.11</v>
+        <v>-12.64</v>
       </c>
       <c r="L18" t="n">
         <v>13.1</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>11.16</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43083</v>
+        <v>43084</v>
       </c>
       <c r="H19" t="n">
-        <v>115.53</v>
+        <v>116.53</v>
       </c>
       <c r="I19" t="n">
         <v>115.8813005743036</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.71</v>
+        <v>-7.63</v>
       </c>
       <c r="L19" t="n">
-        <v>7.02</v>
+        <v>8.77</v>
       </c>
       <c r="M19" t="n">
         <v>1.38</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>7.43</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43101</v>
+        <v>43102</v>
       </c>
       <c r="H20" t="n">
-        <v>109.21</v>
+        <v>108.08</v>
       </c>
       <c r="I20" t="n">
         <v>108.2570009607299</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>-6.28</v>
+        <v>-7.25</v>
       </c>
       <c r="L20" t="n">
-        <v>7.01</v>
+        <v>7.99</v>
       </c>
       <c r="M20" t="n">
         <v>0.53</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>7.9</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43129</v>
+        <v>43130</v>
       </c>
       <c r="H21" t="n">
-        <v>112.26</v>
+        <v>117.53</v>
       </c>
       <c r="I21" t="n">
         <v>113.9245934095644</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.87</v>
+        <v>-8.74</v>
       </c>
       <c r="L21" t="n">
-        <v>4.17</v>
+        <v>10.5</v>
       </c>
       <c r="M21" t="n">
         <v>3.59</v>
       </c>
       <c r="N21" t="n">
-        <v>2.38</v>
+        <v>4.69</v>
       </c>
       <c r="O21" t="n">
         <v>-1.03</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.34</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43138</v>
+        <v>43139</v>
       </c>
       <c r="H22" t="n">
-        <v>113.87</v>
+        <v>107.85</v>
       </c>
       <c r="I22" t="n">
         <v>109.4364306065903</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.11</v>
+        <v>-8.24</v>
       </c>
       <c r="L22" t="n">
-        <v>4.53</v>
+        <v>8.41</v>
       </c>
       <c r="M22" t="n">
-        <v>1.98</v>
+        <v>4.43</v>
       </c>
       <c r="N22" t="n">
-        <v>2.5</v>
+        <v>5.29</v>
       </c>
       <c r="O22" t="n">
         <v>4.69</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>10.34</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43168</v>
+        <v>43171</v>
       </c>
       <c r="H23" t="n">
-        <v>107.8</v>
+        <v>112.59</v>
       </c>
       <c r="I23" t="n">
         <v>109.4074484155448</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>0.05</v>
+        <v>-4.39</v>
       </c>
       <c r="L23" t="n">
-        <v>2.1</v>
+        <v>5.1</v>
       </c>
       <c r="M23" t="n">
         <v>1.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.55</v>
+        <v>4.44</v>
       </c>
       <c r="O23" t="n">
         <v>-5.29</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>9.24</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43174</v>
+        <v>43175</v>
       </c>
       <c r="H24" t="n">
-        <v>107.37</v>
+        <v>102.71</v>
       </c>
       <c r="I24" t="n">
         <v>105.7555540742163</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.64</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>6.24</v>
+        <v>9.44</v>
       </c>
       <c r="M24" t="n">
         <v>3.73</v>
       </c>
       <c r="N24" t="n">
-        <v>3.52</v>
+        <v>4.34</v>
       </c>
       <c r="O24" t="n">
         <v>4.44</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>12.75</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43245</v>
+        <v>43248</v>
       </c>
       <c r="H25" t="n">
-        <v>89.23</v>
+        <v>93.69</v>
       </c>
       <c r="I25" t="n">
         <v>93.27441634663015</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K25" t="n">
-        <v>13.12</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L25" t="n">
         <v>4.81</v>
       </c>
       <c r="M25" t="n">
-        <v>1.87</v>
+        <v>4.68</v>
       </c>
       <c r="N25" t="n">
         <v>5.62</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>11.21</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H26" t="n">
-        <v>91.36</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>87.65275515215238</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.49</v>
+        <v>-10.03</v>
       </c>
       <c r="L26" t="n">
-        <v>4.61</v>
+        <v>10.74</v>
       </c>
       <c r="M26" t="n">
         <v>1.59</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>7.74</v>
       </c>
       <c r="O26" t="n">
         <v>5</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>16.47</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43312</v>
+        <v>43313</v>
       </c>
       <c r="H27" t="n">
-        <v>89.8</v>
+        <v>92.13</v>
       </c>
       <c r="I27" t="n">
         <v>92.1209006220007</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.54</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L27" t="n">
         <v>10.14</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>10.5</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43333</v>
+        <v>43335</v>
       </c>
       <c r="H28" t="n">
-        <v>85.62</v>
+        <v>82.86</v>
       </c>
       <c r="I28" t="n">
         <v>84.2294294359173</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>-7.07</v>
+        <v>-10.06</v>
       </c>
       <c r="L28" t="n">
-        <v>7.23</v>
+        <v>11.15</v>
       </c>
       <c r="M28" t="n">
         <v>0.88</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.19</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H29" t="n">
-        <v>82.95999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I29" t="n">
         <v>85.44397383875919</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.12</v>
+        <v>-3.67</v>
       </c>
       <c r="L29" t="n">
-        <v>4.19</v>
+        <v>4.54</v>
       </c>
       <c r="M29" t="n">
         <v>1.91</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>10.18</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43376</v>
+        <v>43377</v>
       </c>
       <c r="H30" t="n">
-        <v>86.04000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I30" t="n">
         <v>77.15495773795108</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K30" t="n">
-        <v>0.16</v>
+        <v>-13.15</v>
       </c>
       <c r="L30" t="n">
-        <v>6.02</v>
+        <v>23.15</v>
       </c>
       <c r="M30" t="n">
         <v>1.92</v>
       </c>
       <c r="N30" t="n">
-        <v>2.37</v>
+        <v>13.3</v>
       </c>
       <c r="O30" t="n">
         <v>3.54</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>20.51</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43405</v>
+        <v>43406</v>
       </c>
       <c r="H31" t="n">
-        <v>75.55</v>
+        <v>79.63</v>
       </c>
       <c r="I31" t="n">
         <v>78.22203311873866</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.27</v>
+        <v>-6.74</v>
       </c>
       <c r="L31" t="n">
         <v>15.27</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>15.93</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43467</v>
+        <v>43468</v>
       </c>
       <c r="H32" t="n">
-        <v>72.65000000000001</v>
+        <v>69.75</v>
       </c>
       <c r="I32" t="n">
         <v>70.31886278752253</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K32" t="n">
-        <v>-8.77</v>
+        <v>-12.41</v>
       </c>
       <c r="L32" t="n">
         <v>16.51</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.48</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43517</v>
+        <v>43518</v>
       </c>
       <c r="H33" t="n">
-        <v>68.76000000000001</v>
+        <v>72.61</v>
       </c>
       <c r="I33" t="n">
         <v>72.53215064806882</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K33" t="n">
-        <v>1.42</v>
+        <v>-4.1</v>
       </c>
       <c r="L33" t="n">
         <v>6.28</v>
@@ -2322,7 +2717,7 @@
         <v>2.27</v>
       </c>
       <c r="N33" t="n">
-        <v>3.71</v>
+        <v>5.6</v>
       </c>
       <c r="O33" t="n">
         <v>-3.99</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>13.45</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43595</v>
+        <v>43598</v>
       </c>
       <c r="H34" t="n">
-        <v>79.2</v>
+        <v>76.02</v>
       </c>
       <c r="I34" t="n">
         <v>78.52868782199432</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K34" t="n">
-        <v>9.08</v>
+        <v>4.7</v>
       </c>
       <c r="L34" t="n">
         <v>4.78</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>13.24</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H35" t="n">
-        <v>80.48999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="I35" t="n">
         <v>84.76195489086967</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>-5.88</v>
+        <v>-12.56</v>
       </c>
       <c r="L35" t="n">
-        <v>8.380000000000001</v>
+        <v>13.56</v>
       </c>
       <c r="M35" t="n">
-        <v>1.11</v>
+        <v>4.25</v>
       </c>
       <c r="N35" t="n">
-        <v>4.37</v>
+        <v>6.31</v>
       </c>
       <c r="O35" t="n">
         <v>-4.02</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>13.83</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43637</v>
+        <v>43640</v>
       </c>
       <c r="H36" t="n">
-        <v>83.15000000000001</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="I36" t="n">
         <v>82.20621872522787</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.83</v>
+        <v>-4.16</v>
       </c>
       <c r="L36" t="n">
-        <v>4.84</v>
+        <v>5.05</v>
       </c>
       <c r="M36" t="n">
         <v>2.07</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.26</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H37" t="n">
-        <v>65.68000000000001</v>
+        <v>69.67</v>
       </c>
       <c r="I37" t="n">
         <v>69.00157581367776</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K37" t="n">
-        <v>19.91</v>
+        <v>15.05</v>
       </c>
       <c r="L37" t="n">
         <v>4.63</v>
@@ -2550,7 +2993,7 @@
         <v>2.34</v>
       </c>
       <c r="N37" t="n">
-        <v>6.05</v>
+        <v>6.07</v>
       </c>
       <c r="O37" t="n">
         <v>-1.37</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>17.14</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43776</v>
+        <v>43777</v>
       </c>
       <c r="H38" t="n">
-        <v>71.75</v>
+        <v>70.62</v>
       </c>
       <c r="I38" t="n">
         <v>71.13352254612403</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>2.99</v>
+        <v>1.36</v>
       </c>
       <c r="L38" t="n">
         <v>8.199999999999999</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.93</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43979</v>
+        <v>43980</v>
       </c>
       <c r="H39" t="n">
-        <v>34.95</v>
+        <v>38.41</v>
       </c>
       <c r="I39" t="n">
         <v>37.32317739478025</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K39" t="n">
-        <v>50.51</v>
+        <v>45.61</v>
       </c>
       <c r="L39" t="n">
         <v>5.37</v>
@@ -2664,7 +3131,7 @@
         <v>5.72</v>
       </c>
       <c r="N39" t="n">
-        <v>8.960000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="O39" t="n">
         <v>-1.57</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>8</v>
+      </c>
+      <c r="U39" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>18.97</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44077</v>
+        <v>44078</v>
       </c>
       <c r="H40" t="n">
-        <v>39.65</v>
+        <v>38.89</v>
       </c>
       <c r="I40" t="n">
         <v>39.17273148840565</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K40" t="n">
-        <v>3.23</v>
+        <v>1.25</v>
       </c>
       <c r="L40" t="n">
         <v>9.869999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>11.02</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44141</v>
+        <v>44144</v>
       </c>
       <c r="H41" t="n">
-        <v>36.56</v>
+        <v>37.18</v>
       </c>
       <c r="I41" t="n">
         <v>36.93165184504073</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K41" t="n">
-        <v>5.99</v>
+        <v>4.4</v>
       </c>
       <c r="L41" t="n">
         <v>1.72</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H42" t="n">
-        <v>45.25</v>
+        <v>40.89</v>
       </c>
       <c r="I42" t="n">
         <v>42.35674479232976</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K42" t="n">
-        <v>21.71</v>
+        <v>9.98</v>
       </c>
       <c r="L42" t="n">
         <v>1.91</v>
@@ -2835,7 +3338,7 @@
         <v>2.01</v>
       </c>
       <c r="N42" t="n">
-        <v>2.56</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="O42" t="n">
         <v>1.7</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>17.24</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44203</v>
+        <v>44204</v>
       </c>
       <c r="H43" t="n">
-        <v>45.58</v>
+        <v>46.63</v>
       </c>
       <c r="I43" t="n">
         <v>46.50668474175244</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K43" t="n">
-        <v>-11.47</v>
+        <v>-14.04</v>
       </c>
       <c r="L43" t="n">
-        <v>13.23</v>
+        <v>14.4</v>
       </c>
       <c r="M43" t="n">
         <v>1.26</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>10.22</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44218</v>
+        <v>44221</v>
       </c>
       <c r="H44" t="n">
-        <v>46.35</v>
+        <v>44.92</v>
       </c>
       <c r="I44" t="n">
         <v>45.05191829239355</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.6</v>
+        <v>-3.67</v>
       </c>
       <c r="L44" t="n">
-        <v>2.14</v>
+        <v>4.07</v>
       </c>
       <c r="M44" t="n">
         <v>0.49</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>15.18</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H45" t="n">
-        <v>48.29</v>
+        <v>50.24</v>
       </c>
       <c r="I45" t="n">
         <v>49.42744194027538</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>-7.5</v>
+        <v>-11.84</v>
       </c>
       <c r="L45" t="n">
-        <v>8.15</v>
+        <v>12.58</v>
       </c>
       <c r="M45" t="n">
         <v>3.62</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>12.84</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44239</v>
+        <v>44242</v>
       </c>
       <c r="H46" t="n">
-        <v>45.97</v>
+        <v>45.35</v>
       </c>
       <c r="I46" t="n">
         <v>45.6610460075363</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K46" t="n">
-        <v>-8.5</v>
+        <v>-9.73</v>
       </c>
       <c r="L46" t="n">
-        <v>9.18</v>
+        <v>9.93</v>
       </c>
       <c r="M46" t="n">
         <v>5.24</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>13.66</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44260</v>
+        <v>44263</v>
       </c>
       <c r="H47" t="n">
-        <v>50.01</v>
+        <v>51.34</v>
       </c>
       <c r="I47" t="n">
         <v>51.21260598133802</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>-10.28</v>
+        <v>-13.21</v>
       </c>
       <c r="L47" t="n">
-        <v>13.94</v>
+        <v>15.19</v>
       </c>
       <c r="M47" t="n">
         <v>3.99</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.5</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44279</v>
+        <v>44280</v>
       </c>
       <c r="H48" t="n">
-        <v>45.63</v>
+        <v>43.3</v>
       </c>
       <c r="I48" t="n">
         <v>45.4368983319871</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>-11.12</v>
+        <v>-15.66</v>
       </c>
       <c r="L48" t="n">
-        <v>11.47</v>
+        <v>16.21</v>
       </c>
       <c r="M48" t="n">
         <v>2.53</v>
       </c>
       <c r="N48" t="n">
-        <v>3.7</v>
+        <v>5.11</v>
       </c>
       <c r="O48" t="n">
         <v>2.66</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>16.13</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44322</v>
+        <v>44323</v>
       </c>
       <c r="H49" t="n">
-        <v>44.4</v>
+        <v>45.73</v>
       </c>
       <c r="I49" t="n">
         <v>45.69738923078473</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.54</v>
+        <v>-5.61</v>
       </c>
       <c r="L49" t="n">
-        <v>5.61</v>
+        <v>6.37</v>
       </c>
       <c r="M49" t="n">
         <v>1.97</v>
       </c>
       <c r="N49" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
         <v>-5.11</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.51</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44375</v>
+        <v>44376</v>
       </c>
       <c r="H50" t="n">
-        <v>55.94</v>
+        <v>54.23</v>
       </c>
       <c r="I50" t="n">
         <v>54.28293467532076</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K50" t="n">
-        <v>22.33</v>
+        <v>18.59</v>
       </c>
       <c r="L50" t="n">
         <v>3.52</v>
@@ -3291,7 +3890,7 @@
         <v>1.27</v>
       </c>
       <c r="N50" t="n">
-        <v>2.91</v>
+        <v>3.06</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.98</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44438</v>
+        <v>44439</v>
       </c>
       <c r="H51" t="n">
-        <v>53.7</v>
+        <v>55.94</v>
       </c>
       <c r="I51" t="n">
         <v>54.92298296559154</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K51" t="n">
-        <v>0.98</v>
+        <v>-3.15</v>
       </c>
       <c r="L51" t="n">
         <v>4.39</v>
@@ -3348,7 +3959,7 @@
         <v>1.75</v>
       </c>
       <c r="N51" t="n">
-        <v>3.63</v>
+        <v>4.17</v>
       </c>
       <c r="O51" t="n">
         <v>-3.06</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.82</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44516</v>
+        <v>44517</v>
       </c>
       <c r="H52" t="n">
-        <v>68.70999999999999</v>
+        <v>67.09</v>
       </c>
       <c r="I52" t="n">
         <v>67.35447508523889</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K52" t="n">
-        <v>22.83</v>
+        <v>19.93</v>
       </c>
       <c r="L52" t="n">
         <v>3.91</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>11.41</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44567</v>
+        <v>44568</v>
       </c>
       <c r="H53" t="n">
-        <v>59.97</v>
+        <v>60.78</v>
       </c>
       <c r="I53" t="n">
         <v>60.20909377540041</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K53" t="n">
-        <v>10.61</v>
+        <v>9.41</v>
       </c>
       <c r="L53" t="n">
         <v>2.77</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>8.85</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44603</v>
+        <v>44606</v>
       </c>
       <c r="H54" t="n">
-        <v>63.01</v>
+        <v>59.55</v>
       </c>
       <c r="I54" t="n">
         <v>60.44626342536657</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K54" t="n">
-        <v>3.67</v>
+        <v>-2.02</v>
       </c>
       <c r="L54" t="n">
-        <v>1.63</v>
+        <v>2.42</v>
       </c>
       <c r="M54" t="n">
         <v>2.88</v>
       </c>
       <c r="N54" t="n">
-        <v>3.65</v>
+        <v>5.49</v>
       </c>
       <c r="O54" t="n">
         <v>1.35</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>12.68</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44630</v>
+        <v>44631</v>
       </c>
       <c r="H55" t="n">
-        <v>62.35</v>
+        <v>64.06</v>
       </c>
       <c r="I55" t="n">
         <v>63.75360037864191</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.7</v>
+        <v>-7.57</v>
       </c>
       <c r="L55" t="n">
-        <v>7.89</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M55" t="n">
         <v>3.43</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>13.37</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H56" t="n">
-        <v>65.68000000000001</v>
+        <v>64.25</v>
       </c>
       <c r="I56" t="n">
         <v>65.20954493981567</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K56" t="n">
-        <v>2.53</v>
+        <v>0.3</v>
       </c>
       <c r="L56" t="n">
         <v>7.49</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>10.81</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44869</v>
+        <v>44872</v>
       </c>
       <c r="H57" t="n">
-        <v>50.81</v>
+        <v>52.33</v>
       </c>
       <c r="I57" t="n">
         <v>51.60781018385501</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K57" t="n">
-        <v>20.92</v>
+        <v>18.55</v>
       </c>
       <c r="L57" t="n">
         <v>2.29</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>125</v>
+        <v>126</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>7</v>
+      </c>
+      <c r="U57" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.66</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H58" t="n">
-        <v>57.08</v>
+        <v>55.08</v>
       </c>
       <c r="I58" t="n">
         <v>55.84415046116796</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K58" t="n">
-        <v>9.08</v>
+        <v>5.26</v>
       </c>
       <c r="L58" t="n">
         <v>2.54</v>
@@ -3747,7 +4442,7 @@
         <v>1.33</v>
       </c>
       <c r="N58" t="n">
-        <v>2.23</v>
+        <v>3.5</v>
       </c>
       <c r="O58" t="n">
         <v>2.99</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>10.27</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44930</v>
+        <v>44931</v>
       </c>
       <c r="H59" t="n">
-        <v>59.92</v>
+        <v>60.87</v>
       </c>
       <c r="I59" t="n">
         <v>60.4557800857898</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K59" t="n">
-        <v>-8.789999999999999</v>
+        <v>-10.51</v>
       </c>
       <c r="L59" t="n">
         <v>11.2</v>
       </c>
       <c r="M59" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="N59" t="n">
         <v>2.94</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44958</v>
+        <v>44959</v>
       </c>
       <c r="H60" t="n">
-        <v>61.54</v>
+        <v>60.35</v>
       </c>
       <c r="I60" t="n">
         <v>60.57677630869475</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K60" t="n">
-        <v>1.1</v>
+        <v>-0.85</v>
       </c>
       <c r="L60" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="M60" t="n">
         <v>0.39</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.76</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45002</v>
+        <v>45005</v>
       </c>
       <c r="H61" t="n">
-        <v>61.07</v>
+        <v>62.3</v>
       </c>
       <c r="I61" t="n">
         <v>62.20596565190075</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.19</v>
+        <v>-3.23</v>
       </c>
       <c r="L61" t="n">
         <v>3.94</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45155</v>
+        <v>45156</v>
       </c>
       <c r="H62" t="n">
-        <v>76.20999999999999</v>
+        <v>75.41</v>
       </c>
       <c r="I62" t="n">
         <v>75.73033074143534</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K62" t="n">
-        <v>22.33</v>
+        <v>21.04</v>
       </c>
       <c r="L62" t="n">
         <v>7.4</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>6</v>
+      </c>
+      <c r="U62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>6.26</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45176</v>
+        <v>45177</v>
       </c>
       <c r="H63" t="n">
-        <v>75.69</v>
+        <v>77.87</v>
       </c>
       <c r="I63" t="n">
         <v>77.5828566019903</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.37</v>
+        <v>-3.26</v>
       </c>
       <c r="L63" t="n">
-        <v>2.33</v>
+        <v>4.47</v>
       </c>
       <c r="M63" t="n">
         <v>0.63</v>
       </c>
       <c r="N63" t="n">
-        <v>1.66</v>
+        <v>2.88</v>
       </c>
       <c r="O63" t="n">
         <v>-1.05</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>6.67</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45196</v>
+        <v>45197</v>
       </c>
       <c r="H64" t="n">
-        <v>74.45999999999999</v>
+        <v>73.89</v>
       </c>
       <c r="I64" t="n">
         <v>74.25908232958167</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K64" t="n">
-        <v>-4.38</v>
+        <v>-5.11</v>
       </c>
       <c r="L64" t="n">
-        <v>4.74</v>
+        <v>5.48</v>
       </c>
       <c r="M64" t="n">
         <v>0.36</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>7.51</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45230</v>
+        <v>45231</v>
       </c>
       <c r="H65" t="n">
-        <v>73.79000000000001</v>
+        <v>76.41</v>
       </c>
       <c r="I65" t="n">
         <v>75.80656600279869</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K65" t="n">
-        <v>0.14</v>
+        <v>-3.41</v>
       </c>
       <c r="L65" t="n">
-        <v>3.48</v>
+        <v>4.1</v>
       </c>
       <c r="M65" t="n">
-        <v>1.75</v>
+        <v>2.97</v>
       </c>
       <c r="N65" t="n">
-        <v>1.89</v>
+        <v>3.55</v>
       </c>
       <c r="O65" t="n">
         <v>-0.77</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>8.06</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="H66" t="n">
-        <v>157.89</v>
+        <v>152.33</v>
       </c>
       <c r="I66" t="n">
         <v>152.5974862875252</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K66" t="n">
-        <v>106.64</v>
+        <v>99.36</v>
       </c>
       <c r="L66" t="n">
         <v>2.49</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>15.78</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c r="H67" t="n">
-        <v>147.59</v>
+        <v>159.84</v>
       </c>
       <c r="I67" t="n">
         <v>158.5443106888755</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K67" t="n">
-        <v>3.11</v>
+        <v>-4.93</v>
       </c>
       <c r="L67" t="n">
         <v>7.73</v>
       </c>
       <c r="M67" t="n">
-        <v>2.07</v>
+        <v>5.4</v>
       </c>
       <c r="N67" t="n">
-        <v>4.48</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O67" t="n">
         <v>-3.52</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>10.51</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H68" t="n">
-        <v>159.84</v>
+        <v>140.09</v>
       </c>
       <c r="I68" t="n">
         <v>143.044120380012</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>0</v>
+        <v>-12.36</v>
       </c>
       <c r="L68" t="n">
-        <v>4.34</v>
+        <v>15.63</v>
       </c>
       <c r="M68" t="n">
         <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>12.36</v>
       </c>
       <c r="O68" t="n">
         <v>8.300000000000001</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>20.35</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45485</v>
+        <v>45488</v>
       </c>
       <c r="H69" t="n">
-        <v>158.64</v>
+        <v>161.17</v>
       </c>
       <c r="I69" t="n">
         <v>160.2108137496522</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K69" t="n">
-        <v>-13.24</v>
+        <v>-15.05</v>
       </c>
       <c r="L69" t="n">
-        <v>15.25</v>
+        <v>15.46</v>
       </c>
       <c r="M69" t="n">
         <v>3.12</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>6.92</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H70" t="n">
-        <v>162.02</v>
+        <v>158.61</v>
       </c>
       <c r="I70" t="n">
         <v>158.9497141467751</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K70" t="n">
-        <v>0.53</v>
+        <v>-1.59</v>
       </c>
       <c r="L70" t="n">
         <v>5.33</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>12.4</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45539</v>
+        <v>45540</v>
       </c>
       <c r="H71" t="n">
-        <v>168.13</v>
+        <v>172.22</v>
       </c>
       <c r="I71" t="n">
         <v>170.2726020951611</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K71" t="n">
-        <v>-6</v>
+        <v>-8.58</v>
       </c>
       <c r="L71" t="n">
-        <v>8.5</v>
+        <v>10.17</v>
       </c>
       <c r="M71" t="n">
         <v>2.53</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>6.79</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45552</v>
+        <v>45553</v>
       </c>
       <c r="H72" t="n">
-        <v>161.94</v>
+        <v>159.98</v>
       </c>
       <c r="I72" t="n">
         <v>160.524619448742</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.97</v>
+        <v>-7.11</v>
       </c>
       <c r="L72" t="n">
-        <v>6.75</v>
+        <v>7.58</v>
       </c>
       <c r="M72" t="n">
         <v>0.65</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>7.42</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="H73" t="n">
-        <v>162.74</v>
+        <v>170.96</v>
       </c>
       <c r="I73" t="n">
         <v>169.7150366395414</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.73</v>
+        <v>-6.86</v>
       </c>
       <c r="L73" t="n">
-        <v>2.05</v>
+        <v>7.3</v>
       </c>
       <c r="M73" t="n">
         <v>0.3</v>
       </c>
       <c r="N73" t="n">
-        <v>1.61</v>
+        <v>5.05</v>
       </c>
       <c r="O73" t="n">
         <v>-1.21</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45569</v>
+        <v>45572</v>
       </c>
       <c r="H74" t="n">
-        <v>160.17</v>
+        <v>154.55</v>
       </c>
       <c r="I74" t="n">
         <v>157.768663520421</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K74" t="n">
-        <v>-6.31</v>
+        <v>-9.6</v>
       </c>
       <c r="L74" t="n">
-        <v>8.01</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M74" t="n">
         <v>3.26</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>11.98</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="H75" t="n">
-        <v>135.18</v>
+        <v>136.32</v>
       </c>
       <c r="I75" t="n">
         <v>136.0906367144042</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K75" t="n">
-        <v>12.53</v>
+        <v>11.8</v>
       </c>
       <c r="L75" t="n">
         <v>5.48</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>6.54</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H76" t="n">
-        <v>129.39</v>
+        <v>127.84</v>
       </c>
       <c r="I76" t="n">
         <v>128.3133249216847</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K76" t="n">
-        <v>-5.08</v>
+        <v>-6.22</v>
       </c>
       <c r="L76" t="n">
         <v>6.97</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,25 +5732,25 @@
         <v>7.73</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45721</v>
+        <v>45722</v>
       </c>
       <c r="H77" t="n">
-        <v>116.1</v>
+        <v>119.52</v>
       </c>
       <c r="I77" t="n">
         <v>117.0076712393674</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K77" t="n">
-        <v>9.18</v>
+        <v>6.51</v>
       </c>
       <c r="L77" t="n">
         <v>3.88</v>
       </c>
       <c r="M77" t="n">
-        <v>1.44</v>
+        <v>1.92</v>
       </c>
       <c r="N77" t="n">
         <v>3.8</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,19 +5801,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45869</v>
+        <v>45870</v>
       </c>
       <c r="H78" t="n">
-        <v>138.3</v>
+        <v>133.94</v>
       </c>
       <c r="I78" t="n">
         <v>137.8978954907245</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K78" t="n">
-        <v>15.71</v>
+        <v>12.06</v>
       </c>
       <c r="L78" t="n">
         <v>4.38</v>
@@ -4887,7 +5822,7 @@
         <v>5.9</v>
       </c>
       <c r="N78" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="O78" t="n">
         <v>2.95</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>6</v>
+      </c>
+      <c r="U78" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>8.49</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H79" t="n">
-        <v>140.67</v>
+        <v>141.6</v>
       </c>
       <c r="I79" t="n">
         <v>141.1371592247214</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K79" t="n">
-        <v>-5.02</v>
+        <v>-5.72</v>
       </c>
       <c r="L79" t="n">
-        <v>5.32</v>
+        <v>6.66</v>
       </c>
       <c r="M79" t="n">
         <v>1.34</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>4.58</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="H80" t="n">
-        <v>158.94</v>
+        <v>156.94</v>
       </c>
       <c r="I80" t="n">
         <v>157.3492737229843</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K80" t="n">
-        <v>12.25</v>
+        <v>10.83</v>
       </c>
       <c r="L80" t="n">
         <v>1.47</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -5037,28 +6008,28 @@
         <v>6.31</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="H81" t="n">
-        <v>161.57</v>
+        <v>166.46</v>
       </c>
       <c r="I81" t="n">
         <v>165.8340871444606</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K81" t="n">
-        <v>-2.95</v>
+        <v>-6.07</v>
       </c>
       <c r="L81" t="n">
-        <v>5.45</v>
+        <v>6.62</v>
       </c>
       <c r="M81" t="n">
         <v>0.92</v>
       </c>
       <c r="N81" t="n">
-        <v>2.98</v>
+        <v>3.03</v>
       </c>
       <c r="O81" t="n">
         <v>-1.26</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,28 +6077,28 @@
         <v>6.92</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="H82" t="n">
-        <v>162.67</v>
+        <v>156.37</v>
       </c>
       <c r="I82" t="n">
         <v>157.0878906109946</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K82" t="n">
-        <v>-2.28</v>
+        <v>-6.06</v>
       </c>
       <c r="L82" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="M82" t="n">
         <v>0.19</v>
       </c>
       <c r="N82" t="n">
-        <v>1.07</v>
+        <v>3.87</v>
       </c>
       <c r="O82" t="n">
         <v>3.03</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S82" t="b">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -5151,28 +6146,28 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H83" t="n">
-        <v>167.58</v>
+        <v>172.78</v>
       </c>
       <c r="I83" t="n">
         <v>167.6376275992222</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K83" t="n">
-        <v>-7.17</v>
+        <v>-10.49</v>
       </c>
       <c r="L83" t="n">
-        <v>7.88</v>
+        <v>11.08</v>
       </c>
       <c r="M83" t="n">
         <v>2.36</v>
       </c>
       <c r="N83" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="O83" t="n">
         <v>-3.87</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>2</v>
+      </c>
+      <c r="U83" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>9.41</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H84" t="n">
-        <v>179.11</v>
+        <v>170.44</v>
       </c>
       <c r="I84" t="n">
         <v>175.3130500462393</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K84" t="n">
-        <v>3.66</v>
+        <v>-1.35</v>
       </c>
       <c r="L84" t="n">
         <v>3.74</v>
@@ -5229,7 +6236,7 @@
         <v>3.29</v>
       </c>
       <c r="N84" t="n">
-        <v>4.46</v>
+        <v>4.84</v>
       </c>
       <c r="O84" t="n">
         <v>3.1</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>2</v>
+      </c>
+      <c r="U84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -5265,19 +6284,19 @@
         <v>10.47</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="H85" t="n">
-        <v>140.94</v>
+        <v>144.49</v>
       </c>
       <c r="I85" t="n">
         <v>144.4676153134403</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K85" t="n">
-        <v>17.31</v>
+        <v>15.23</v>
       </c>
       <c r="L85" t="n">
         <v>3.36</v>
@@ -5295,7 +6314,19 @@
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S85" t="b">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>4</v>
+      </c>
+      <c r="U85" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>7.32</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H86" t="n">
-        <v>137.6</v>
+        <v>135.15</v>
       </c>
       <c r="I86" t="n">
         <v>135.4349216643328</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K86" t="n">
-        <v>-4.77</v>
+        <v>-6.46</v>
       </c>
       <c r="L86" t="n">
         <v>7.04</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>4</v>
+      </c>
+      <c r="U86" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -5403,6 +6446,14 @@
       <c r="Q87" t="n">
         <v>35</v>
       </c>
+      <c r="R87" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10361,7 +11412,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -10371,7 +11422,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -10381,7 +11432,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8">
@@ -10391,7 +11442,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -10401,7 +11452,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -10411,7 +11462,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98.8</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -10421,7 +11472,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -10431,7 +11482,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -10441,7 +11492,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -10451,7 +11502,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.67</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="15">
@@ -10461,7 +11512,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.37</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="16">
@@ -10471,7 +11522,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="17">
@@ -10481,7 +11532,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>106.64</v>
+        <v>99.36</v>
       </c>
     </row>
     <row r="18">
@@ -10491,7 +11542,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.9</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="19">
@@ -10501,7 +11552,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.25</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="20">
@@ -10511,7 +11562,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.32</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="21">
@@ -10521,7 +11572,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>16.51</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="22">
@@ -10531,7 +11582,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23">
@@ -10541,7 +11592,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -10551,7 +11602,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="25">
@@ -10571,7 +11622,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.02</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="27">
@@ -10581,7 +11632,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.960000000000001</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="28">
@@ -10591,7 +11642,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
